--- a/Excel/LevelConfig.xlsx
+++ b/Excel/LevelConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="37">
   <si>
     <t>Id</t>
   </si>
@@ -45,6 +45,99 @@
   </si>
   <si>
     <t>long</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>90000000000</t>
+  </si>
+  <si>
+    <t>270000000000</t>
+  </si>
+  <si>
+    <t>810000000000</t>
+  </si>
+  <si>
+    <t>2430000000000</t>
+  </si>
+  <si>
+    <t>7200000000000</t>
+  </si>
+  <si>
+    <t>21600000000000</t>
+  </si>
+  <si>
+    <t>64800000000000</t>
+  </si>
+  <si>
+    <t>195000000000000</t>
+  </si>
+  <si>
+    <t>600000000000000</t>
+  </si>
+  <si>
+    <t>1800000000000000</t>
+  </si>
+  <si>
+    <t>5400000000000000</t>
+  </si>
+  <si>
+    <t>16000000000000000</t>
+  </si>
+  <si>
+    <t>48000000000000000</t>
+  </si>
+  <si>
+    <t>150000000000000000</t>
+  </si>
+  <si>
+    <t>300000000000000000</t>
+  </si>
+  <si>
+    <t>600000000000000000</t>
+  </si>
+  <si>
+    <t>1000000000000000000</t>
+  </si>
+  <si>
+    <t>2000000000000000000</t>
+  </si>
+  <si>
+    <t>4000000000000000000</t>
+  </si>
+  <si>
+    <t>8000000000000000000</t>
+  </si>
+  <si>
+    <t>16000000000000000000</t>
+  </si>
+  <si>
+    <t>30000000000000000000</t>
+  </si>
+  <si>
+    <t>60000000000000000000</t>
+  </si>
+  <si>
+    <t>120000000000000000000</t>
+  </si>
+  <si>
+    <t>240000000000000000000</t>
+  </si>
+  <si>
+    <t>480000000000000000000</t>
+  </si>
+  <si>
+    <t>1000000000000000000000</t>
+  </si>
+  <si>
+    <t>2000000000000000000000</t>
+  </si>
+  <si>
+    <t>4000000000000000000000</t>
+  </si>
+  <si>
+    <t>8000000000000000000000</t>
   </si>
 </sst>
 </file>
@@ -688,6 +781,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1036,20 +1130,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:F19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
+  <dimension ref="C3:F64"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="21.125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.75" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="21.1272727272727" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7545454545455" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.87272727272727" style="1" customWidth="1"/>
     <col min="4" max="4" width="9.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9.125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="18.25" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.12727272727273" style="1" customWidth="1"/>
+    <col min="6" max="6" width="31.1818181818182" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.2545454545455" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:6">
+    <row r="3" ht="13.5" spans="3:6">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1063,7 +1157,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="3:6">
+    <row r="4" ht="13.5" spans="3:6">
       <c r="C4" s="2" t="s">
         <v>0</v>
       </c>
@@ -1077,7 +1171,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="3:6">
+    <row r="5" ht="13.5" spans="3:6">
       <c r="C5" s="2" t="s">
         <v>4</v>
       </c>
@@ -1088,7 +1182,7 @@
         <v>5</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="3:6">
@@ -1110,7 +1204,7 @@
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <f t="shared" ref="D7:D19" si="0">E6+1</f>
+        <f t="shared" ref="D7:D64" si="0">E6+1</f>
         <v>101</v>
       </c>
       <c r="E7" s="1">
@@ -1298,6 +1392,692 @@
       </c>
       <c r="F19" s="1">
         <v>23000</v>
+      </c>
+    </row>
+    <row r="20" spans="3:6">
+      <c r="C20" s="1">
+        <v>15</v>
+      </c>
+      <c r="D20" s="1">
+        <f t="shared" si="0"/>
+        <v>80001</v>
+      </c>
+      <c r="E20" s="1">
+        <v>100000</v>
+      </c>
+      <c r="F20" s="1">
+        <v>28000</v>
+      </c>
+    </row>
+    <row r="21" spans="3:6">
+      <c r="C21" s="1">
+        <v>16</v>
+      </c>
+      <c r="D21" s="1">
+        <f t="shared" si="0"/>
+        <v>100001</v>
+      </c>
+      <c r="E21" s="1">
+        <v>120000</v>
+      </c>
+      <c r="F21" s="1">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="22" spans="3:6">
+      <c r="C22" s="1">
+        <v>17</v>
+      </c>
+      <c r="D22" s="1">
+        <f t="shared" si="0"/>
+        <v>120001</v>
+      </c>
+      <c r="E22" s="1">
+        <v>130000</v>
+      </c>
+      <c r="F22" s="1">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="23" spans="3:6">
+      <c r="C23" s="1">
+        <v>18</v>
+      </c>
+      <c r="D23" s="1">
+        <f t="shared" si="0"/>
+        <v>130001</v>
+      </c>
+      <c r="E23" s="1">
+        <v>140000</v>
+      </c>
+      <c r="F23" s="1">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="24" spans="3:6">
+      <c r="C24" s="1">
+        <v>19</v>
+      </c>
+      <c r="D24" s="1">
+        <f t="shared" si="0"/>
+        <v>140001</v>
+      </c>
+      <c r="E24" s="1">
+        <v>150000</v>
+      </c>
+      <c r="F24" s="1">
+        <f t="shared" ref="F24:F37" si="1">F23*3</f>
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="25" spans="3:6">
+      <c r="C25" s="1">
+        <v>20</v>
+      </c>
+      <c r="D25" s="1">
+        <f t="shared" si="0"/>
+        <v>150001</v>
+      </c>
+      <c r="E25" s="1">
+        <v>160000</v>
+      </c>
+      <c r="F25" s="1">
+        <f t="shared" si="1"/>
+        <v>1800000</v>
+      </c>
+    </row>
+    <row r="26" spans="3:6">
+      <c r="C26" s="1">
+        <v>21</v>
+      </c>
+      <c r="D26" s="1">
+        <f t="shared" si="0"/>
+        <v>160001</v>
+      </c>
+      <c r="E26" s="1">
+        <v>170000</v>
+      </c>
+      <c r="F26" s="1">
+        <f t="shared" si="1"/>
+        <v>5400000</v>
+      </c>
+    </row>
+    <row r="27" spans="3:6">
+      <c r="C27" s="1">
+        <v>22</v>
+      </c>
+      <c r="D27" s="1">
+        <f t="shared" si="0"/>
+        <v>170001</v>
+      </c>
+      <c r="E27" s="1">
+        <v>180000</v>
+      </c>
+      <c r="F27" s="1">
+        <f t="shared" si="1"/>
+        <v>16200000</v>
+      </c>
+    </row>
+    <row r="28" spans="3:6">
+      <c r="C28" s="1">
+        <v>23</v>
+      </c>
+      <c r="D28" s="1">
+        <f t="shared" si="0"/>
+        <v>180001</v>
+      </c>
+      <c r="E28" s="1">
+        <v>190000</v>
+      </c>
+      <c r="F28" s="1">
+        <f t="shared" si="1"/>
+        <v>48600000</v>
+      </c>
+    </row>
+    <row r="29" spans="3:6">
+      <c r="C29" s="1">
+        <v>24</v>
+      </c>
+      <c r="D29" s="1">
+        <f t="shared" si="0"/>
+        <v>190001</v>
+      </c>
+      <c r="E29" s="1">
+        <v>200000</v>
+      </c>
+      <c r="F29" s="1">
+        <f t="shared" si="1"/>
+        <v>145800000</v>
+      </c>
+    </row>
+    <row r="30" spans="3:6">
+      <c r="C30" s="1">
+        <v>25</v>
+      </c>
+      <c r="D30" s="1">
+        <f t="shared" si="0"/>
+        <v>200001</v>
+      </c>
+      <c r="E30" s="1">
+        <v>210000</v>
+      </c>
+      <c r="F30" s="1">
+        <f t="shared" si="1"/>
+        <v>437400000</v>
+      </c>
+    </row>
+    <row r="31" spans="3:6">
+      <c r="C31" s="1">
+        <v>26</v>
+      </c>
+      <c r="D31" s="1">
+        <f t="shared" si="0"/>
+        <v>210001</v>
+      </c>
+      <c r="E31" s="1">
+        <v>220000</v>
+      </c>
+      <c r="F31" s="1">
+        <f t="shared" si="1"/>
+        <v>1312200000</v>
+      </c>
+    </row>
+    <row r="32" spans="3:6">
+      <c r="C32" s="1">
+        <v>27</v>
+      </c>
+      <c r="D32" s="1">
+        <f t="shared" si="0"/>
+        <v>220001</v>
+      </c>
+      <c r="E32" s="1">
+        <v>230000</v>
+      </c>
+      <c r="F32" s="1">
+        <f t="shared" si="1"/>
+        <v>3936600000</v>
+      </c>
+    </row>
+    <row r="33" spans="3:6">
+      <c r="C33" s="1">
+        <v>28</v>
+      </c>
+      <c r="D33" s="1">
+        <f t="shared" si="0"/>
+        <v>230001</v>
+      </c>
+      <c r="E33" s="1">
+        <v>250000</v>
+      </c>
+      <c r="F33" s="1">
+        <f t="shared" si="1"/>
+        <v>11809800000</v>
+      </c>
+    </row>
+    <row r="34" spans="3:6">
+      <c r="C34" s="1">
+        <v>29</v>
+      </c>
+      <c r="D34" s="1">
+        <f t="shared" si="0"/>
+        <v>250001</v>
+      </c>
+      <c r="E34" s="1">
+        <v>260000</v>
+      </c>
+      <c r="F34" s="1">
+        <f t="shared" si="1"/>
+        <v>35429400000</v>
+      </c>
+    </row>
+    <row r="35" spans="3:6">
+      <c r="C35" s="1">
+        <v>30</v>
+      </c>
+      <c r="D35" s="1">
+        <f t="shared" si="0"/>
+        <v>260001</v>
+      </c>
+      <c r="E35" s="1">
+        <v>270000</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="3:6">
+      <c r="C36" s="1">
+        <v>31</v>
+      </c>
+      <c r="D36" s="1">
+        <f t="shared" si="0"/>
+        <v>270001</v>
+      </c>
+      <c r="E36" s="1">
+        <v>280000</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="3:6">
+      <c r="C37" s="1">
+        <v>32</v>
+      </c>
+      <c r="D37" s="1">
+        <f t="shared" si="0"/>
+        <v>280001</v>
+      </c>
+      <c r="E37" s="1">
+        <v>290000</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="3:6">
+      <c r="C38" s="1">
+        <v>33</v>
+      </c>
+      <c r="D38" s="1">
+        <f t="shared" si="0"/>
+        <v>290001</v>
+      </c>
+      <c r="E38" s="1">
+        <v>300000</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="3:6">
+      <c r="C39" s="1">
+        <v>34</v>
+      </c>
+      <c r="D39" s="1">
+        <f t="shared" si="0"/>
+        <v>300001</v>
+      </c>
+      <c r="E39" s="1">
+        <v>310000</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="3:6">
+      <c r="C40" s="1">
+        <v>35</v>
+      </c>
+      <c r="D40" s="1">
+        <f t="shared" si="0"/>
+        <v>310001</v>
+      </c>
+      <c r="E40" s="1">
+        <v>320000</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" spans="3:6">
+      <c r="C41" s="1">
+        <v>36</v>
+      </c>
+      <c r="D41" s="1">
+        <f t="shared" si="0"/>
+        <v>320001</v>
+      </c>
+      <c r="E41" s="1">
+        <v>330000</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="3:6">
+      <c r="C42" s="1">
+        <v>37</v>
+      </c>
+      <c r="D42" s="1">
+        <f t="shared" si="0"/>
+        <v>330001</v>
+      </c>
+      <c r="E42" s="1">
+        <v>340000</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" spans="3:6">
+      <c r="C43" s="1">
+        <v>38</v>
+      </c>
+      <c r="D43" s="1">
+        <f t="shared" si="0"/>
+        <v>340001</v>
+      </c>
+      <c r="E43" s="1">
+        <v>350000</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="3:6">
+      <c r="C44" s="1">
+        <v>39</v>
+      </c>
+      <c r="D44" s="1">
+        <f t="shared" si="0"/>
+        <v>350001</v>
+      </c>
+      <c r="E44" s="1">
+        <v>360000</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="3:6">
+      <c r="C45" s="1">
+        <v>40</v>
+      </c>
+      <c r="D45" s="1">
+        <f t="shared" si="0"/>
+        <v>360001</v>
+      </c>
+      <c r="E45" s="1">
+        <v>370000</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46" spans="3:6">
+      <c r="C46" s="1">
+        <v>41</v>
+      </c>
+      <c r="D46" s="1">
+        <f t="shared" si="0"/>
+        <v>370001</v>
+      </c>
+      <c r="E46" s="1">
+        <v>380000</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="3:6">
+      <c r="C47" s="1">
+        <v>42</v>
+      </c>
+      <c r="D47" s="1">
+        <f t="shared" si="0"/>
+        <v>380001</v>
+      </c>
+      <c r="E47" s="1">
+        <v>390000</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="48" spans="3:6">
+      <c r="C48" s="1">
+        <v>43</v>
+      </c>
+      <c r="D48" s="1">
+        <f t="shared" si="0"/>
+        <v>390001</v>
+      </c>
+      <c r="E48" s="1">
+        <v>400000</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="49" spans="3:6">
+      <c r="C49" s="1">
+        <v>44</v>
+      </c>
+      <c r="D49" s="1">
+        <f t="shared" si="0"/>
+        <v>400001</v>
+      </c>
+      <c r="E49" s="1">
+        <v>410000</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="50" spans="3:6">
+      <c r="C50" s="1">
+        <v>45</v>
+      </c>
+      <c r="D50" s="1">
+        <f t="shared" si="0"/>
+        <v>410001</v>
+      </c>
+      <c r="E50" s="1">
+        <v>420000</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="51" spans="3:6">
+      <c r="C51" s="1">
+        <v>46</v>
+      </c>
+      <c r="D51" s="1">
+        <f t="shared" si="0"/>
+        <v>420001</v>
+      </c>
+      <c r="E51" s="1">
+        <v>430000</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="52" spans="3:6">
+      <c r="C52" s="1">
+        <v>47</v>
+      </c>
+      <c r="D52" s="1">
+        <f t="shared" si="0"/>
+        <v>430001</v>
+      </c>
+      <c r="E52" s="1">
+        <v>440000</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="53" spans="3:6">
+      <c r="C53" s="1">
+        <v>48</v>
+      </c>
+      <c r="D53" s="1">
+        <f t="shared" si="0"/>
+        <v>440001</v>
+      </c>
+      <c r="E53" s="1">
+        <v>450000</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="54" spans="3:6">
+      <c r="C54" s="1">
+        <v>49</v>
+      </c>
+      <c r="D54" s="1">
+        <f t="shared" si="0"/>
+        <v>450001</v>
+      </c>
+      <c r="E54" s="1">
+        <v>460000</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="55" spans="3:6">
+      <c r="C55" s="1">
+        <v>50</v>
+      </c>
+      <c r="D55" s="1">
+        <f t="shared" si="0"/>
+        <v>460001</v>
+      </c>
+      <c r="E55" s="1">
+        <v>470000</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="56" spans="3:6">
+      <c r="C56" s="1">
+        <v>51</v>
+      </c>
+      <c r="D56" s="1">
+        <f t="shared" si="0"/>
+        <v>470001</v>
+      </c>
+      <c r="E56" s="1">
+        <v>480000</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="57" spans="3:6">
+      <c r="C57" s="1">
+        <v>52</v>
+      </c>
+      <c r="D57" s="1">
+        <f t="shared" si="0"/>
+        <v>480001</v>
+      </c>
+      <c r="E57" s="1">
+        <v>490000</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="58" spans="3:6">
+      <c r="C58" s="1">
+        <v>53</v>
+      </c>
+      <c r="D58" s="1">
+        <f t="shared" si="0"/>
+        <v>490001</v>
+      </c>
+      <c r="E58" s="1">
+        <v>500000</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="59" spans="3:6">
+      <c r="C59" s="1">
+        <v>54</v>
+      </c>
+      <c r="D59" s="1">
+        <f t="shared" si="0"/>
+        <v>500001</v>
+      </c>
+      <c r="E59" s="1">
+        <v>510000</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="60" spans="3:6">
+      <c r="C60" s="1">
+        <v>55</v>
+      </c>
+      <c r="D60" s="1">
+        <f t="shared" si="0"/>
+        <v>510001</v>
+      </c>
+      <c r="E60" s="1">
+        <v>520000</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="61" spans="3:6">
+      <c r="C61" s="1">
+        <v>56</v>
+      </c>
+      <c r="D61" s="1">
+        <f t="shared" si="0"/>
+        <v>520001</v>
+      </c>
+      <c r="E61" s="1">
+        <v>530000</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="62" spans="3:6">
+      <c r="C62" s="1">
+        <v>57</v>
+      </c>
+      <c r="D62" s="1">
+        <f t="shared" si="0"/>
+        <v>530001</v>
+      </c>
+      <c r="E62" s="1">
+        <v>540000</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="63" spans="3:6">
+      <c r="C63" s="1">
+        <v>58</v>
+      </c>
+      <c r="D63" s="1">
+        <f t="shared" si="0"/>
+        <v>540001</v>
+      </c>
+      <c r="E63" s="1">
+        <v>550000</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="64" spans="3:6">
+      <c r="C64" s="1">
+        <v>59</v>
+      </c>
+      <c r="D64" s="1">
+        <f t="shared" si="0"/>
+        <v>550001</v>
+      </c>
+      <c r="E64" s="1">
+        <v>560000</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/LevelConfig.xlsx
+++ b/Excel/LevelConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
   <si>
     <t>Id</t>
   </si>
@@ -48,96 +48,6 @@
   </si>
   <si>
     <t>string</t>
-  </si>
-  <si>
-    <t>90000000000</t>
-  </si>
-  <si>
-    <t>270000000000</t>
-  </si>
-  <si>
-    <t>810000000000</t>
-  </si>
-  <si>
-    <t>2430000000000</t>
-  </si>
-  <si>
-    <t>7200000000000</t>
-  </si>
-  <si>
-    <t>21600000000000</t>
-  </si>
-  <si>
-    <t>64800000000000</t>
-  </si>
-  <si>
-    <t>195000000000000</t>
-  </si>
-  <si>
-    <t>600000000000000</t>
-  </si>
-  <si>
-    <t>1800000000000000</t>
-  </si>
-  <si>
-    <t>5400000000000000</t>
-  </si>
-  <si>
-    <t>16000000000000000</t>
-  </si>
-  <si>
-    <t>48000000000000000</t>
-  </si>
-  <si>
-    <t>150000000000000000</t>
-  </si>
-  <si>
-    <t>300000000000000000</t>
-  </si>
-  <si>
-    <t>600000000000000000</t>
-  </si>
-  <si>
-    <t>1000000000000000000</t>
-  </si>
-  <si>
-    <t>2000000000000000000</t>
-  </si>
-  <si>
-    <t>4000000000000000000</t>
-  </si>
-  <si>
-    <t>8000000000000000000</t>
-  </si>
-  <si>
-    <t>16000000000000000000</t>
-  </si>
-  <si>
-    <t>30000000000000000000</t>
-  </si>
-  <si>
-    <t>60000000000000000000</t>
-  </si>
-  <si>
-    <t>120000000000000000000</t>
-  </si>
-  <si>
-    <t>240000000000000000000</t>
-  </si>
-  <si>
-    <t>480000000000000000000</t>
-  </si>
-  <si>
-    <t>1000000000000000000000</t>
-  </si>
-  <si>
-    <t>2000000000000000000000</t>
-  </si>
-  <si>
-    <t>4000000000000000000000</t>
-  </si>
-  <si>
-    <t>8000000000000000000000</t>
   </si>
 </sst>
 </file>
@@ -781,7 +691,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1130,15 +1039,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:F64"/>
+  <dimension ref="C3:F14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="21.1272727272727" style="1" customWidth="1"/>
     <col min="2" max="2" width="12.7545454545455" style="1" customWidth="1"/>
     <col min="3" max="3" width="8.87272727272727" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9.12727272727273" style="1" customWidth="1"/>
-    <col min="6" max="6" width="31.1818181818182" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.1818181818182" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.6363636363636" style="1" customWidth="1"/>
     <col min="7" max="7" width="18.2545454545455" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
@@ -1193,7 +1102,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F6" s="1">
         <v>100</v>
@@ -1204,14 +1113,14 @@
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <f t="shared" ref="D7:D64" si="0">E6+1</f>
-        <v>101</v>
+        <f>E6+1</f>
+        <v>11</v>
       </c>
       <c r="E7" s="1">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="F7" s="1">
-        <v>200</v>
+        <v>500</v>
       </c>
     </row>
     <row r="8" spans="3:6">
@@ -1219,14 +1128,14 @@
         <v>3</v>
       </c>
       <c r="D8" s="1">
-        <f t="shared" si="0"/>
-        <v>201</v>
+        <f>E7+1</f>
+        <v>21</v>
       </c>
       <c r="E8" s="1">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="F8" s="1">
-        <v>300</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="9" spans="3:6">
@@ -1234,14 +1143,14 @@
         <v>4</v>
       </c>
       <c r="D9" s="1">
-        <f t="shared" si="0"/>
-        <v>501</v>
+        <f>E8+1</f>
+        <v>31</v>
       </c>
       <c r="E9" s="1">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="F9" s="1">
-        <v>600</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="10" spans="3:6">
@@ -1249,14 +1158,14 @@
         <v>5</v>
       </c>
       <c r="D10" s="1">
-        <f t="shared" si="0"/>
-        <v>1001</v>
+        <f>E9+1</f>
+        <v>51</v>
       </c>
       <c r="E10" s="1">
-        <v>2000</v>
+        <v>80</v>
       </c>
       <c r="F10" s="1">
-        <v>1000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="11" spans="3:6">
@@ -1264,14 +1173,14 @@
         <v>6</v>
       </c>
       <c r="D11" s="1">
-        <f t="shared" si="0"/>
-        <v>2001</v>
+        <f>E10+1</f>
+        <v>81</v>
       </c>
       <c r="E11" s="1">
-        <v>5000</v>
+        <v>120</v>
       </c>
       <c r="F11" s="1">
-        <v>1500</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="12" spans="3:6">
@@ -1279,14 +1188,14 @@
         <v>7</v>
       </c>
       <c r="D12" s="1">
-        <f t="shared" si="0"/>
-        <v>5001</v>
+        <f>E11+1</f>
+        <v>121</v>
       </c>
       <c r="E12" s="1">
-        <v>10000</v>
+        <v>160</v>
       </c>
       <c r="F12" s="1">
-        <v>2100</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="13" spans="3:6">
@@ -1294,14 +1203,14 @@
         <v>8</v>
       </c>
       <c r="D13" s="1">
-        <f t="shared" si="0"/>
-        <v>10001</v>
+        <f>E12+1</f>
+        <v>161</v>
       </c>
       <c r="E13" s="1">
-        <v>20000</v>
+        <v>200</v>
       </c>
       <c r="F13" s="1">
-        <v>2800</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="14" spans="3:6">
@@ -1309,775 +1218,14 @@
         <v>9</v>
       </c>
       <c r="D14" s="1">
-        <f t="shared" si="0"/>
-        <v>20001</v>
+        <f>E13+1</f>
+        <v>201</v>
       </c>
       <c r="E14" s="1">
-        <v>30000</v>
+        <v>300</v>
       </c>
       <c r="F14" s="1">
-        <v>2100</v>
-      </c>
-    </row>
-    <row r="15" spans="3:6">
-      <c r="C15" s="1">
-        <v>10</v>
-      </c>
-      <c r="D15" s="1">
-        <f t="shared" si="0"/>
-        <v>30001</v>
-      </c>
-      <c r="E15" s="1">
-        <v>40000</v>
-      </c>
-      <c r="F15" s="1">
-        <v>4500</v>
-      </c>
-    </row>
-    <row r="16" spans="3:6">
-      <c r="C16" s="1">
-        <v>11</v>
-      </c>
-      <c r="D16" s="1">
-        <f t="shared" si="0"/>
-        <v>40001</v>
-      </c>
-      <c r="E16" s="1">
-        <v>50000</v>
-      </c>
-      <c r="F16" s="1">
-        <v>8000</v>
-      </c>
-    </row>
-    <row r="17" spans="3:6">
-      <c r="C17" s="1">
-        <v>12</v>
-      </c>
-      <c r="D17" s="1">
-        <f t="shared" si="0"/>
-        <v>50001</v>
-      </c>
-      <c r="E17" s="1">
-        <v>60000</v>
-      </c>
-      <c r="F17" s="1">
-        <v>13000</v>
-      </c>
-    </row>
-    <row r="18" spans="3:6">
-      <c r="C18" s="1">
-        <v>13</v>
-      </c>
-      <c r="D18" s="1">
-        <f t="shared" si="0"/>
-        <v>60001</v>
-      </c>
-      <c r="E18" s="1">
-        <v>70000</v>
-      </c>
-      <c r="F18" s="1">
-        <v>18000</v>
-      </c>
-    </row>
-    <row r="19" spans="3:6">
-      <c r="C19" s="1">
-        <v>14</v>
-      </c>
-      <c r="D19" s="1">
-        <f t="shared" si="0"/>
-        <v>70001</v>
-      </c>
-      <c r="E19" s="1">
-        <v>80000</v>
-      </c>
-      <c r="F19" s="1">
-        <v>23000</v>
-      </c>
-    </row>
-    <row r="20" spans="3:6">
-      <c r="C20" s="1">
-        <v>15</v>
-      </c>
-      <c r="D20" s="1">
-        <f t="shared" si="0"/>
-        <v>80001</v>
-      </c>
-      <c r="E20" s="1">
-        <v>100000</v>
-      </c>
-      <c r="F20" s="1">
-        <v>28000</v>
-      </c>
-    </row>
-    <row r="21" spans="3:6">
-      <c r="C21" s="1">
-        <v>16</v>
-      </c>
-      <c r="D21" s="1">
-        <f t="shared" si="0"/>
-        <v>100001</v>
-      </c>
-      <c r="E21" s="1">
-        <v>120000</v>
-      </c>
-      <c r="F21" s="1">
-        <v>33000</v>
-      </c>
-    </row>
-    <row r="22" spans="3:6">
-      <c r="C22" s="1">
-        <v>17</v>
-      </c>
-      <c r="D22" s="1">
-        <f t="shared" si="0"/>
-        <v>120001</v>
-      </c>
-      <c r="E22" s="1">
-        <v>130000</v>
-      </c>
-      <c r="F22" s="1">
-        <v>70000</v>
-      </c>
-    </row>
-    <row r="23" spans="3:6">
-      <c r="C23" s="1">
-        <v>18</v>
-      </c>
-      <c r="D23" s="1">
-        <f t="shared" si="0"/>
-        <v>130001</v>
-      </c>
-      <c r="E23" s="1">
-        <v>140000</v>
-      </c>
-      <c r="F23" s="1">
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="24" spans="3:6">
-      <c r="C24" s="1">
-        <v>19</v>
-      </c>
-      <c r="D24" s="1">
-        <f t="shared" si="0"/>
-        <v>140001</v>
-      </c>
-      <c r="E24" s="1">
-        <v>150000</v>
-      </c>
-      <c r="F24" s="1">
-        <f t="shared" ref="F24:F37" si="1">F23*3</f>
-        <v>600000</v>
-      </c>
-    </row>
-    <row r="25" spans="3:6">
-      <c r="C25" s="1">
-        <v>20</v>
-      </c>
-      <c r="D25" s="1">
-        <f t="shared" si="0"/>
-        <v>150001</v>
-      </c>
-      <c r="E25" s="1">
-        <v>160000</v>
-      </c>
-      <c r="F25" s="1">
-        <f t="shared" si="1"/>
-        <v>1800000</v>
-      </c>
-    </row>
-    <row r="26" spans="3:6">
-      <c r="C26" s="1">
-        <v>21</v>
-      </c>
-      <c r="D26" s="1">
-        <f t="shared" si="0"/>
-        <v>160001</v>
-      </c>
-      <c r="E26" s="1">
-        <v>170000</v>
-      </c>
-      <c r="F26" s="1">
-        <f t="shared" si="1"/>
-        <v>5400000</v>
-      </c>
-    </row>
-    <row r="27" spans="3:6">
-      <c r="C27" s="1">
-        <v>22</v>
-      </c>
-      <c r="D27" s="1">
-        <f t="shared" si="0"/>
-        <v>170001</v>
-      </c>
-      <c r="E27" s="1">
-        <v>180000</v>
-      </c>
-      <c r="F27" s="1">
-        <f t="shared" si="1"/>
-        <v>16200000</v>
-      </c>
-    </row>
-    <row r="28" spans="3:6">
-      <c r="C28" s="1">
-        <v>23</v>
-      </c>
-      <c r="D28" s="1">
-        <f t="shared" si="0"/>
-        <v>180001</v>
-      </c>
-      <c r="E28" s="1">
-        <v>190000</v>
-      </c>
-      <c r="F28" s="1">
-        <f t="shared" si="1"/>
-        <v>48600000</v>
-      </c>
-    </row>
-    <row r="29" spans="3:6">
-      <c r="C29" s="1">
-        <v>24</v>
-      </c>
-      <c r="D29" s="1">
-        <f t="shared" si="0"/>
-        <v>190001</v>
-      </c>
-      <c r="E29" s="1">
-        <v>200000</v>
-      </c>
-      <c r="F29" s="1">
-        <f t="shared" si="1"/>
-        <v>145800000</v>
-      </c>
-    </row>
-    <row r="30" spans="3:6">
-      <c r="C30" s="1">
-        <v>25</v>
-      </c>
-      <c r="D30" s="1">
-        <f t="shared" si="0"/>
-        <v>200001</v>
-      </c>
-      <c r="E30" s="1">
-        <v>210000</v>
-      </c>
-      <c r="F30" s="1">
-        <f t="shared" si="1"/>
-        <v>437400000</v>
-      </c>
-    </row>
-    <row r="31" spans="3:6">
-      <c r="C31" s="1">
-        <v>26</v>
-      </c>
-      <c r="D31" s="1">
-        <f t="shared" si="0"/>
-        <v>210001</v>
-      </c>
-      <c r="E31" s="1">
-        <v>220000</v>
-      </c>
-      <c r="F31" s="1">
-        <f t="shared" si="1"/>
-        <v>1312200000</v>
-      </c>
-    </row>
-    <row r="32" spans="3:6">
-      <c r="C32" s="1">
-        <v>27</v>
-      </c>
-      <c r="D32" s="1">
-        <f t="shared" si="0"/>
-        <v>220001</v>
-      </c>
-      <c r="E32" s="1">
-        <v>230000</v>
-      </c>
-      <c r="F32" s="1">
-        <f t="shared" si="1"/>
-        <v>3936600000</v>
-      </c>
-    </row>
-    <row r="33" spans="3:6">
-      <c r="C33" s="1">
-        <v>28</v>
-      </c>
-      <c r="D33" s="1">
-        <f t="shared" si="0"/>
-        <v>230001</v>
-      </c>
-      <c r="E33" s="1">
-        <v>250000</v>
-      </c>
-      <c r="F33" s="1">
-        <f t="shared" si="1"/>
-        <v>11809800000</v>
-      </c>
-    </row>
-    <row r="34" spans="3:6">
-      <c r="C34" s="1">
-        <v>29</v>
-      </c>
-      <c r="D34" s="1">
-        <f t="shared" si="0"/>
-        <v>250001</v>
-      </c>
-      <c r="E34" s="1">
-        <v>260000</v>
-      </c>
-      <c r="F34" s="1">
-        <f t="shared" si="1"/>
-        <v>35429400000</v>
-      </c>
-    </row>
-    <row r="35" spans="3:6">
-      <c r="C35" s="1">
-        <v>30</v>
-      </c>
-      <c r="D35" s="1">
-        <f t="shared" si="0"/>
-        <v>260001</v>
-      </c>
-      <c r="E35" s="1">
-        <v>270000</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="36" spans="3:6">
-      <c r="C36" s="1">
-        <v>31</v>
-      </c>
-      <c r="D36" s="1">
-        <f t="shared" si="0"/>
-        <v>270001</v>
-      </c>
-      <c r="E36" s="1">
-        <v>280000</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="37" spans="3:6">
-      <c r="C37" s="1">
-        <v>32</v>
-      </c>
-      <c r="D37" s="1">
-        <f t="shared" si="0"/>
-        <v>280001</v>
-      </c>
-      <c r="E37" s="1">
-        <v>290000</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="38" spans="3:6">
-      <c r="C38" s="1">
-        <v>33</v>
-      </c>
-      <c r="D38" s="1">
-        <f t="shared" si="0"/>
-        <v>290001</v>
-      </c>
-      <c r="E38" s="1">
-        <v>300000</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="39" spans="3:6">
-      <c r="C39" s="1">
-        <v>34</v>
-      </c>
-      <c r="D39" s="1">
-        <f t="shared" si="0"/>
-        <v>300001</v>
-      </c>
-      <c r="E39" s="1">
-        <v>310000</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="40" spans="3:6">
-      <c r="C40" s="1">
-        <v>35</v>
-      </c>
-      <c r="D40" s="1">
-        <f t="shared" si="0"/>
-        <v>310001</v>
-      </c>
-      <c r="E40" s="1">
-        <v>320000</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="41" spans="3:6">
-      <c r="C41" s="1">
-        <v>36</v>
-      </c>
-      <c r="D41" s="1">
-        <f t="shared" si="0"/>
-        <v>320001</v>
-      </c>
-      <c r="E41" s="1">
-        <v>330000</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="42" spans="3:6">
-      <c r="C42" s="1">
-        <v>37</v>
-      </c>
-      <c r="D42" s="1">
-        <f t="shared" si="0"/>
-        <v>330001</v>
-      </c>
-      <c r="E42" s="1">
-        <v>340000</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="43" spans="3:6">
-      <c r="C43" s="1">
-        <v>38</v>
-      </c>
-      <c r="D43" s="1">
-        <f t="shared" si="0"/>
-        <v>340001</v>
-      </c>
-      <c r="E43" s="1">
-        <v>350000</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="44" spans="3:6">
-      <c r="C44" s="1">
-        <v>39</v>
-      </c>
-      <c r="D44" s="1">
-        <f t="shared" si="0"/>
-        <v>350001</v>
-      </c>
-      <c r="E44" s="1">
-        <v>360000</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="45" spans="3:6">
-      <c r="C45" s="1">
-        <v>40</v>
-      </c>
-      <c r="D45" s="1">
-        <f t="shared" si="0"/>
-        <v>360001</v>
-      </c>
-      <c r="E45" s="1">
-        <v>370000</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="46" spans="3:6">
-      <c r="C46" s="1">
-        <v>41</v>
-      </c>
-      <c r="D46" s="1">
-        <f t="shared" si="0"/>
-        <v>370001</v>
-      </c>
-      <c r="E46" s="1">
-        <v>380000</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="47" spans="3:6">
-      <c r="C47" s="1">
-        <v>42</v>
-      </c>
-      <c r="D47" s="1">
-        <f t="shared" si="0"/>
-        <v>380001</v>
-      </c>
-      <c r="E47" s="1">
-        <v>390000</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="48" spans="3:6">
-      <c r="C48" s="1">
-        <v>43</v>
-      </c>
-      <c r="D48" s="1">
-        <f t="shared" si="0"/>
-        <v>390001</v>
-      </c>
-      <c r="E48" s="1">
-        <v>400000</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="49" spans="3:6">
-      <c r="C49" s="1">
-        <v>44</v>
-      </c>
-      <c r="D49" s="1">
-        <f t="shared" si="0"/>
-        <v>400001</v>
-      </c>
-      <c r="E49" s="1">
-        <v>410000</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="50" spans="3:6">
-      <c r="C50" s="1">
-        <v>45</v>
-      </c>
-      <c r="D50" s="1">
-        <f t="shared" si="0"/>
-        <v>410001</v>
-      </c>
-      <c r="E50" s="1">
-        <v>420000</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="51" spans="3:6">
-      <c r="C51" s="1">
-        <v>46</v>
-      </c>
-      <c r="D51" s="1">
-        <f t="shared" si="0"/>
-        <v>420001</v>
-      </c>
-      <c r="E51" s="1">
-        <v>430000</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="52" spans="3:6">
-      <c r="C52" s="1">
-        <v>47</v>
-      </c>
-      <c r="D52" s="1">
-        <f t="shared" si="0"/>
-        <v>430001</v>
-      </c>
-      <c r="E52" s="1">
-        <v>440000</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="53" spans="3:6">
-      <c r="C53" s="1">
-        <v>48</v>
-      </c>
-      <c r="D53" s="1">
-        <f t="shared" si="0"/>
-        <v>440001</v>
-      </c>
-      <c r="E53" s="1">
-        <v>450000</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="54" spans="3:6">
-      <c r="C54" s="1">
-        <v>49</v>
-      </c>
-      <c r="D54" s="1">
-        <f t="shared" si="0"/>
-        <v>450001</v>
-      </c>
-      <c r="E54" s="1">
-        <v>460000</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="55" spans="3:6">
-      <c r="C55" s="1">
-        <v>50</v>
-      </c>
-      <c r="D55" s="1">
-        <f t="shared" si="0"/>
-        <v>460001</v>
-      </c>
-      <c r="E55" s="1">
-        <v>470000</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="56" spans="3:6">
-      <c r="C56" s="1">
-        <v>51</v>
-      </c>
-      <c r="D56" s="1">
-        <f t="shared" si="0"/>
-        <v>470001</v>
-      </c>
-      <c r="E56" s="1">
-        <v>480000</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="57" spans="3:6">
-      <c r="C57" s="1">
-        <v>52</v>
-      </c>
-      <c r="D57" s="1">
-        <f t="shared" si="0"/>
-        <v>480001</v>
-      </c>
-      <c r="E57" s="1">
-        <v>490000</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="58" spans="3:6">
-      <c r="C58" s="1">
-        <v>53</v>
-      </c>
-      <c r="D58" s="1">
-        <f t="shared" si="0"/>
-        <v>490001</v>
-      </c>
-      <c r="E58" s="1">
-        <v>500000</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="59" spans="3:6">
-      <c r="C59" s="1">
-        <v>54</v>
-      </c>
-      <c r="D59" s="1">
-        <f t="shared" si="0"/>
-        <v>500001</v>
-      </c>
-      <c r="E59" s="1">
-        <v>510000</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="60" spans="3:6">
-      <c r="C60" s="1">
-        <v>55</v>
-      </c>
-      <c r="D60" s="1">
-        <f t="shared" si="0"/>
-        <v>510001</v>
-      </c>
-      <c r="E60" s="1">
-        <v>520000</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="61" spans="3:6">
-      <c r="C61" s="1">
-        <v>56</v>
-      </c>
-      <c r="D61" s="1">
-        <f t="shared" si="0"/>
-        <v>520001</v>
-      </c>
-      <c r="E61" s="1">
-        <v>530000</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="62" spans="3:6">
-      <c r="C62" s="1">
-        <v>57</v>
-      </c>
-      <c r="D62" s="1">
-        <f t="shared" si="0"/>
-        <v>530001</v>
-      </c>
-      <c r="E62" s="1">
-        <v>540000</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="63" spans="3:6">
-      <c r="C63" s="1">
-        <v>58</v>
-      </c>
-      <c r="D63" s="1">
-        <f t="shared" si="0"/>
-        <v>540001</v>
-      </c>
-      <c r="E63" s="1">
-        <v>550000</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="64" spans="3:6">
-      <c r="C64" s="1">
-        <v>59</v>
-      </c>
-      <c r="D64" s="1">
-        <f t="shared" si="0"/>
-        <v>550001</v>
-      </c>
-      <c r="E64" s="1">
-        <v>560000</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>36</v>
+        <v>20000000</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/LevelConfig.xlsx
+++ b/Excel/LevelConfig.xlsx
@@ -1113,14 +1113,14 @@
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <f>E6+1</f>
+        <f t="shared" ref="D7:D14" si="0">E6+1</f>
         <v>11</v>
       </c>
       <c r="E7" s="1">
         <v>20</v>
       </c>
       <c r="F7" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="8" spans="3:6">
@@ -1128,14 +1128,14 @@
         <v>3</v>
       </c>
       <c r="D8" s="1">
-        <f>E7+1</f>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="E8" s="1">
         <v>30</v>
       </c>
       <c r="F8" s="1">
-        <v>2000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="9" spans="3:6">
@@ -1143,14 +1143,14 @@
         <v>4</v>
       </c>
       <c r="D9" s="1">
-        <f>E8+1</f>
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="E9" s="1">
         <v>50</v>
       </c>
       <c r="F9" s="1">
-        <v>10000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="10" spans="3:6">
@@ -1158,14 +1158,14 @@
         <v>5</v>
       </c>
       <c r="D10" s="1">
-        <f>E9+1</f>
+        <f t="shared" si="0"/>
         <v>51</v>
       </c>
       <c r="E10" s="1">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F10" s="1">
-        <v>50000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="11" spans="3:6">
@@ -1173,14 +1173,14 @@
         <v>6</v>
       </c>
       <c r="D11" s="1">
-        <f>E10+1</f>
-        <v>81</v>
+        <f t="shared" si="0"/>
+        <v>71</v>
       </c>
       <c r="E11" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F11" s="1">
-        <v>200000</v>
+        <v>400000</v>
       </c>
     </row>
     <row r="12" spans="3:6">
@@ -1188,8 +1188,8 @@
         <v>7</v>
       </c>
       <c r="D12" s="1">
-        <f>E11+1</f>
-        <v>121</v>
+        <f t="shared" si="0"/>
+        <v>101</v>
       </c>
       <c r="E12" s="1">
         <v>160</v>
@@ -1203,7 +1203,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="1">
-        <f>E12+1</f>
+        <f t="shared" si="0"/>
         <v>161</v>
       </c>
       <c r="E13" s="1">
@@ -1218,7 +1218,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="1">
-        <f>E13+1</f>
+        <f t="shared" si="0"/>
         <v>201</v>
       </c>
       <c r="E14" s="1">

--- a/Excel/LevelConfig.xlsx
+++ b/Excel/LevelConfig.xlsx
@@ -1039,8 +1039,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:F14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="5"/>
+  <dimension ref="C3:F22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="21.1272727272727" style="1" customWidth="1"/>
     <col min="2" max="2" width="12.7545454545455" style="1" customWidth="1"/>
@@ -1052,7 +1052,7 @@
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="13.5" spans="3:6">
+    <row r="3" customHeight="1" spans="3:6">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1066,7 +1066,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" ht="13.5" spans="3:6">
+    <row r="4" customHeight="1" spans="3:6">
       <c r="C4" s="2" t="s">
         <v>0</v>
       </c>
@@ -1080,7 +1080,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" ht="13.5" spans="3:6">
+    <row r="5" customHeight="1" spans="3:6">
       <c r="C5" s="2" t="s">
         <v>4</v>
       </c>
@@ -1094,7 +1094,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="3:6">
+    <row r="6" customHeight="1" spans="3:6">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1108,12 +1108,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="3:6">
+    <row r="7" customHeight="1" spans="3:6">
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <f t="shared" ref="D7:D14" si="0">E6+1</f>
+        <f t="shared" ref="D7:D16" si="0">E6+1</f>
         <v>11</v>
       </c>
       <c r="E7" s="1">
@@ -1123,7 +1123,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="8" spans="3:6">
+    <row r="8" customHeight="1" spans="3:6">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1138,7 +1138,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="9" spans="3:6">
+    <row r="9" customHeight="1" spans="3:6">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1147,85 +1147,205 @@
         <v>31</v>
       </c>
       <c r="E9" s="1">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="F9" s="1">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="10" spans="3:6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="3:6">
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="1">
         <f t="shared" si="0"/>
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="E10" s="1">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="F10" s="1">
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="11" spans="3:6">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="3:6">
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" s="1">
         <f t="shared" si="0"/>
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="E11" s="1">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="F11" s="1">
-        <v>400000</v>
-      </c>
-    </row>
-    <row r="12" spans="3:6">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="3:6">
       <c r="C12" s="1">
         <v>7</v>
       </c>
       <c r="D12" s="1">
         <f t="shared" si="0"/>
-        <v>101</v>
+        <v>46</v>
       </c>
       <c r="E12" s="1">
-        <v>160</v>
+        <v>50</v>
       </c>
       <c r="F12" s="1">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="13" spans="3:6">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="3:6">
       <c r="C13" s="1">
         <v>8</v>
       </c>
       <c r="D13" s="1">
         <f t="shared" si="0"/>
-        <v>161</v>
+        <v>51</v>
       </c>
       <c r="E13" s="1">
-        <v>200</v>
+        <v>55</v>
       </c>
       <c r="F13" s="1">
-        <v>5000000</v>
-      </c>
-    </row>
-    <row r="14" spans="3:6">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:6">
       <c r="C14" s="1">
         <v>9</v>
       </c>
       <c r="D14" s="1">
         <f t="shared" si="0"/>
-        <v>201</v>
+        <v>56</v>
       </c>
       <c r="E14" s="1">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="F14" s="1">
-        <v>20000000</v>
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="3:6">
+      <c r="C15" s="1">
+        <v>10</v>
+      </c>
+      <c r="D15" s="1">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+      <c r="E15" s="1">
+        <v>65</v>
+      </c>
+      <c r="F15" s="1">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="3:6">
+      <c r="C16" s="1">
+        <v>11</v>
+      </c>
+      <c r="D16" s="1">
+        <f t="shared" si="0"/>
+        <v>66</v>
+      </c>
+      <c r="E16" s="1">
+        <v>70</v>
+      </c>
+      <c r="F16" s="1">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:6">
+      <c r="C17" s="1">
+        <v>12</v>
+      </c>
+      <c r="D17" s="1">
+        <f>E9+1</f>
+        <v>36</v>
+      </c>
+      <c r="E17" s="1">
+        <v>75</v>
+      </c>
+      <c r="F17" s="1">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="3:6">
+      <c r="C18" s="1">
+        <v>13</v>
+      </c>
+      <c r="D18" s="1">
+        <f t="shared" ref="D18:D22" si="1">E17+1</f>
+        <v>76</v>
+      </c>
+      <c r="E18" s="1">
+        <v>80</v>
+      </c>
+      <c r="F18" s="1">
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="3:6">
+      <c r="C19" s="1">
+        <v>14</v>
+      </c>
+      <c r="D19" s="1">
+        <f t="shared" si="1"/>
+        <v>81</v>
+      </c>
+      <c r="E19" s="1">
+        <v>85</v>
+      </c>
+      <c r="F19" s="1">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="3:6">
+      <c r="C20" s="1">
+        <v>15</v>
+      </c>
+      <c r="D20" s="1">
+        <f t="shared" si="1"/>
+        <v>86</v>
+      </c>
+      <c r="E20" s="1">
+        <v>90</v>
+      </c>
+      <c r="F20" s="1">
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:6">
+      <c r="C21" s="1">
+        <v>16</v>
+      </c>
+      <c r="D21" s="1">
+        <f t="shared" si="1"/>
+        <v>91</v>
+      </c>
+      <c r="E21" s="1">
+        <v>95</v>
+      </c>
+      <c r="F21" s="1">
+        <v>4000000</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="3:6">
+      <c r="C22" s="1">
+        <v>17</v>
+      </c>
+      <c r="D22" s="1">
+        <f t="shared" si="1"/>
+        <v>96</v>
+      </c>
+      <c r="E22" s="1">
+        <v>100</v>
+      </c>
+      <c r="F22" s="1">
+        <v>6000000</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/LevelConfig.xlsx
+++ b/Excel/LevelConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="6">
   <si>
     <t>Id</t>
   </si>
@@ -45,9 +45,6 @@
   </si>
   <si>
     <t>long</t>
-  </si>
-  <si>
-    <t>string</t>
   </si>
 </sst>
 </file>
@@ -1091,7 +1088,7 @@
         <v>5</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="3:6">
@@ -1120,7 +1117,7 @@
         <v>20</v>
       </c>
       <c r="F7" s="1">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:6">
@@ -1135,7 +1132,7 @@
         <v>30</v>
       </c>
       <c r="F8" s="1">
-        <v>5000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:6">
@@ -1150,7 +1147,7 @@
         <v>35</v>
       </c>
       <c r="F9" s="1">
-        <v>10000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:6">
@@ -1165,7 +1162,7 @@
         <v>40</v>
       </c>
       <c r="F10" s="1">
-        <v>20000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:6">
@@ -1180,7 +1177,7 @@
         <v>45</v>
       </c>
       <c r="F11" s="1">
-        <v>40000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:6">
@@ -1195,7 +1192,7 @@
         <v>50</v>
       </c>
       <c r="F12" s="1">
-        <v>60000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:6">
@@ -1210,7 +1207,7 @@
         <v>55</v>
       </c>
       <c r="F13" s="1">
-        <v>80000</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:6">
@@ -1225,7 +1222,7 @@
         <v>60</v>
       </c>
       <c r="F14" s="1">
-        <v>100000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:6">
@@ -1240,7 +1237,7 @@
         <v>65</v>
       </c>
       <c r="F15" s="1">
-        <v>200000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:6">
@@ -1255,7 +1252,7 @@
         <v>70</v>
       </c>
       <c r="F16" s="1">
-        <v>400000</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:6">
@@ -1270,7 +1267,7 @@
         <v>75</v>
       </c>
       <c r="F17" s="1">
-        <v>600000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:6">
@@ -1285,7 +1282,7 @@
         <v>80</v>
       </c>
       <c r="F18" s="1">
-        <v>800000</v>
+        <v>400000</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:6">
@@ -1300,7 +1297,7 @@
         <v>85</v>
       </c>
       <c r="F19" s="1">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:6">
@@ -1315,7 +1312,7 @@
         <v>90</v>
       </c>
       <c r="F20" s="1">
-        <v>2000000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:6">
@@ -1330,7 +1327,7 @@
         <v>95</v>
       </c>
       <c r="F21" s="1">
-        <v>4000000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:6">
@@ -1345,7 +1342,7 @@
         <v>100</v>
       </c>
       <c r="F22" s="1">
-        <v>6000000</v>
+        <v>3000000</v>
       </c>
     </row>
   </sheetData>
